--- a/docs/wo2.xlsx
+++ b/docs/wo2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FE86BE-B1C3-4C4F-A39E-2A992669642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527542B6-3AD6-4440-9ABB-C2D4921922EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C32645C5-10AA-4D5C-BF11-217FF2F37ECD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="273">
   <si>
     <t>Pause Barbell Lunge</t>
   </si>
@@ -847,6 +847,15 @@
   </si>
   <si>
     <t>Hamstrings, Shoulders</t>
+  </si>
+  <si>
+    <t>Half Kneeling bottoms up KB Press</t>
+  </si>
+  <si>
+    <t>Seated Lat Raise</t>
+  </si>
+  <si>
+    <t>Push Press</t>
   </si>
 </sst>
 </file>
@@ -862,12 +871,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -882,8 +897,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1751,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A791CA79-5EDF-4534-95D3-2767A2C8696F}">
-  <dimension ref="A2:S142"/>
+  <dimension ref="A2:S158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -3605,6 +3621,102 @@
         <v>269</v>
       </c>
     </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>101</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>101</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>101</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>91</v>
+      </c>
+      <c r="B147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>91</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>91</v>
+      </c>
+      <c r="B149" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>93</v>
+      </c>
+      <c r="B151" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>99</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>99</v>
+      </c>
+      <c r="B154" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>168</v>
+      </c>
+      <c r="B156" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>99</v>
+      </c>
+      <c r="B158" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
